--- a/docs/StructureDefinition-body-weight.xlsx
+++ b/docs/StructureDefinition-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-body-weight.xlsx
+++ b/docs/StructureDefinition-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-body-weight.xlsx
+++ b/docs/StructureDefinition-body-weight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3701" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3701" uniqueCount="652">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -484,25 +484,29 @@
     <t>A code representing the the type of device used for this observation.  Should only be used if not implicit in the code found in `Observation.code`.</t>
   </si>
   <si>
-    <t>Observation.extension:measurmentDevice.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:measurmentDevice.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>example</t>
@@ -571,10 +575,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Observation.extension:measurmentDevice.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -603,10 +603,6 @@
     <t>Observation.extension:associatedSituation.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Observation.extension:associatedSituation.extension</t>
   </si>
   <si>
@@ -627,9 +623,6 @@
   </si>
   <si>
     <t>Observation.extension:associatedSituation.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Observation.extension:associatedSituation.value[x]:valueCodeableConcept</t>
@@ -3597,7 +3590,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3623,10 +3616,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3649,13 +3642,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3706,7 +3699,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3715,7 +3708,7 @@
         <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
@@ -3730,7 +3723,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3741,10 +3734,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3815,7 +3808,7 @@
         <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
@@ -3824,7 +3817,7 @@
         <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3859,10 +3852,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3888,13 +3881,13 @@
         <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3902,7 +3895,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -3944,7 +3937,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -3979,10 +3972,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4005,13 +3998,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4038,27 +4031,27 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4067,7 +4060,7 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -4096,7 +4089,7 @@
         <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>180</v>
@@ -4121,13 +4114,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4176,7 +4169,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4185,7 +4178,7 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -4334,7 +4327,7 @@
         <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4357,13 +4350,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4414,7 +4407,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4438,7 +4431,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4449,14 +4442,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4478,13 +4471,13 @@
         <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4525,7 +4518,7 @@
         <v>141</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4534,7 +4527,7 @@
         <v>142</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4558,7 +4551,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4569,10 +4562,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4598,13 +4591,13 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4654,7 +4647,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>93</v>
@@ -4689,10 +4682,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4715,13 +4708,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4760,17 +4753,17 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4805,10 +4798,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>180</v>
@@ -4833,13 +4826,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4870,7 +4863,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4888,7 +4881,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4923,13 +4916,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>137</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>20</v>
@@ -4951,10 +4944,10 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>140</v>
@@ -5043,14 +5036,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5072,16 +5065,16 @@
         <v>138</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -5130,7 +5123,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5165,10 +5158,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5191,17 +5184,17 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5250,7 +5243,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5265,19 +5258,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -5285,14 +5278,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5311,17 +5304,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5370,7 +5363,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5385,16 +5378,16 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5405,14 +5398,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5431,16 +5424,16 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5490,7 +5483,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5505,16 +5498,16 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5525,10 +5518,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5554,16 +5547,16 @@
         <v>113</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5588,11 +5581,11 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5610,7 +5603,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>93</v>
@@ -5625,19 +5618,19 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>20</v>
@@ -5645,10 +5638,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5671,19 +5664,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5711,16 +5704,16 @@
         <v>117</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5730,7 +5723,7 @@
         <v>142</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5754,10 +5747,10 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -5765,13 +5758,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
@@ -5793,19 +5786,19 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5833,10 +5826,10 @@
         <v>117</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5854,7 +5847,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5878,10 +5871,10 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5889,10 +5882,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5915,13 +5908,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5972,7 +5965,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5996,7 +5989,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6007,14 +6000,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6036,13 +6029,13 @@
         <v>138</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6083,7 +6076,7 @@
         <v>141</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>20</v>
@@ -6092,7 +6085,7 @@
         <v>142</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6116,7 +6109,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6127,10 +6120,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6153,19 +6146,19 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -6214,7 +6207,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6235,10 +6228,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6249,10 +6242,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6275,13 +6268,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6332,7 +6325,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6356,7 +6349,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6367,14 +6360,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6396,13 +6389,13 @@
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6443,7 +6436,7 @@
         <v>141</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
@@ -6452,7 +6445,7 @@
         <v>142</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6476,7 +6469,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6487,10 +6480,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6516,23 +6509,23 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>20</v>
@@ -6574,7 +6567,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6595,10 +6588,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6609,10 +6602,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6635,16 +6628,16 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6694,7 +6687,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6715,10 +6708,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6729,10 +6722,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6758,21 +6751,21 @@
         <v>113</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>20</v>
@@ -6814,7 +6807,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6835,10 +6828,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6849,10 +6842,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6875,17 +6868,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6934,7 +6927,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6955,10 +6948,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6969,10 +6962,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6995,19 +6988,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7056,7 +7049,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7077,10 +7070,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7091,10 +7084,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7117,19 +7110,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7178,7 +7171,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7199,10 +7192,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7213,14 +7206,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7239,19 +7232,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7279,10 +7272,10 @@
         <v>181</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -7300,7 +7293,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>93</v>
@@ -7315,30 +7308,30 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7361,13 +7354,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7418,7 +7411,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7442,7 +7435,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7453,14 +7446,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7482,13 +7475,13 @@
         <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7529,7 +7522,7 @@
         <v>141</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>20</v>
@@ -7538,7 +7531,7 @@
         <v>142</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7562,7 +7555,7 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7573,10 +7566,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7599,19 +7592,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7648,7 +7641,7 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7658,7 +7651,7 @@
         <v>142</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7679,10 +7672,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7693,13 +7686,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
@@ -7721,19 +7714,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7782,7 +7775,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7803,10 +7796,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7817,10 +7810,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7843,13 +7836,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7900,7 +7893,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7924,7 +7917,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7935,14 +7928,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7964,13 +7957,13 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8011,7 +8004,7 @@
         <v>141</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
@@ -8020,7 +8013,7 @@
         <v>142</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8044,7 +8037,7 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8055,10 +8048,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8084,23 +8077,23 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>20</v>
@@ -8142,7 +8135,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8163,10 +8156,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8177,10 +8170,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8203,16 +8196,16 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8262,7 +8255,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8283,10 +8276,10 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8297,10 +8290,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8326,21 +8319,21 @@
         <v>113</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>20</v>
@@ -8382,7 +8375,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8403,10 +8396,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8417,10 +8410,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8443,17 +8436,17 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8502,7 +8495,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8523,10 +8516,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8537,10 +8530,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8563,19 +8556,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8624,7 +8617,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8645,10 +8638,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8659,10 +8652,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8685,19 +8678,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8746,7 +8739,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8767,10 +8760,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8781,10 +8774,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8807,19 +8800,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8868,7 +8861,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8883,19 +8876,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>20</v>
@@ -8903,10 +8896,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8929,16 +8922,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8988,7 +8981,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9009,13 +9002,13 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>20</v>
@@ -9023,14 +9016,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9049,19 +9042,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9110,7 +9103,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9125,19 +9118,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>20</v>
@@ -9145,14 +9138,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9171,19 +9164,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9232,7 +9225,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9241,25 +9234,25 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AK57" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AK57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -9267,10 +9260,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9293,16 +9286,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9352,7 +9345,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9373,13 +9366,13 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9387,10 +9380,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9413,17 +9406,17 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9472,7 +9465,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9487,19 +9480,19 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9507,10 +9500,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9533,19 +9526,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9582,17 +9575,17 @@
         <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9601,7 +9594,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9610,30 +9603,30 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>20</v>
@@ -9655,19 +9648,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9716,7 +9709,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9725,7 +9718,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9734,27 +9727,27 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9777,13 +9770,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9834,7 +9827,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9858,7 +9851,7 @@
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9869,14 +9862,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9898,13 +9891,13 @@
         <v>138</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9945,7 +9938,7 @@
         <v>141</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>20</v>
@@ -9954,7 +9947,7 @@
         <v>142</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9978,7 +9971,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9989,10 +9982,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10015,19 +10008,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10076,7 +10069,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10097,10 +10090,10 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10111,10 +10104,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10140,65 +10133,65 @@
         <v>113</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="R65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y65" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="P65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q65" t="s" s="2">
+      <c r="Z65" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="R65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Y65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10219,10 +10212,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10233,10 +10226,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10259,17 +10252,17 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10318,7 +10311,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10339,10 +10332,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10353,10 +10346,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10382,72 +10375,72 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10459,10 +10452,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10473,10 +10466,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10502,16 +10495,16 @@
         <v>113</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O68" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10536,11 +10529,11 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -10558,7 +10551,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10579,10 +10572,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10593,10 +10586,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10619,19 +10612,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10659,37 +10652,37 @@
         <v>181</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10704,7 +10697,7 @@
         <v>136</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10715,14 +10708,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10741,19 +10734,19 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10782,7 +10775,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10800,7 +10793,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10818,27 +10811,27 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10861,19 +10854,19 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10922,7 +10915,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10943,10 +10936,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10957,10 +10950,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10983,16 +10976,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11018,13 +11011,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -11042,7 +11035,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11060,27 +11053,27 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11103,19 +11096,19 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11140,13 +11133,13 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -11164,7 +11157,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11185,10 +11178,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11199,10 +11192,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11225,16 +11218,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11284,7 +11277,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11302,27 +11295,27 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11345,16 +11338,16 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11404,7 +11397,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11422,27 +11415,27 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11465,19 +11458,19 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11526,7 +11519,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11538,19 +11531,19 @@
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11561,10 +11554,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11587,13 +11580,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11644,7 +11637,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11668,7 +11661,7 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11679,14 +11672,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11708,13 +11701,13 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11764,7 +11757,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11788,7 +11781,7 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11799,14 +11792,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11828,16 +11821,16 @@
         <v>138</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11886,7 +11879,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11921,10 +11914,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11947,13 +11940,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12004,7 +11997,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12013,7 +12006,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12025,10 +12018,10 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12039,10 +12032,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12065,13 +12058,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12122,7 +12115,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12131,7 +12124,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12143,10 +12136,10 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12157,10 +12150,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12183,19 +12176,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12223,10 +12216,10 @@
         <v>117</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -12244,7 +12237,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12262,13 +12255,13 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12279,10 +12272,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12305,19 +12298,19 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12342,13 +12335,13 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -12366,7 +12359,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12384,13 +12377,13 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12401,10 +12394,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12427,17 +12420,17 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12486,7 +12479,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12510,7 +12503,7 @@
         <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12521,10 +12514,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12547,13 +12540,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12604,7 +12597,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12625,10 +12618,10 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12639,10 +12632,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12665,16 +12658,16 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12724,7 +12717,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12745,10 +12738,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12759,10 +12752,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12785,16 +12778,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12844,7 +12837,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12865,10 +12858,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12879,10 +12872,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12905,19 +12898,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O88" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12966,7 +12959,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12978,19 +12971,19 @@
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13001,10 +12994,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13027,13 +13020,13 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13084,7 +13077,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13108,7 +13101,7 @@
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13119,14 +13112,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13148,13 +13141,13 @@
         <v>138</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13204,7 +13197,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13228,7 +13221,7 @@
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13239,14 +13232,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13268,16 +13261,16 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13326,7 +13319,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13361,10 +13354,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13387,19 +13380,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13427,10 +13420,10 @@
         <v>181</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13448,7 +13441,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>93</v>
@@ -13466,16 +13459,16 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>20</v>
@@ -13483,10 +13476,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13509,19 +13502,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>638</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13549,37 +13542,37 @@
         <v>181</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI93" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13588,27 +13581,27 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13631,19 +13624,19 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M94" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13671,10 +13664,10 @@
         <v>181</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
@@ -13692,7 +13685,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13701,7 +13694,7 @@
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13716,7 +13709,7 @@
         <v>136</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -13727,14 +13720,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13753,19 +13746,19 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13793,10 +13786,10 @@
         <v>181</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
@@ -13814,7 +13807,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13832,27 +13825,27 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13878,16 +13871,16 @@
         <v>20</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13936,7 +13929,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13957,10 +13950,10 @@
         <v>20</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-body-weight.xlsx
+++ b/docs/StructureDefinition-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
